--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -84,6 +84,129 @@
   </si>
   <si>
     <t>注释</t>
+  </si>
+  <si>
+    <t>ItemType</t>
+  </si>
+  <si>
+    <t>道具类型</t>
+  </si>
+  <si>
+    <t>Consume</t>
+  </si>
+  <si>
+    <t>消耗</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>材料</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>装备</t>
+  </si>
+  <si>
+    <t>ItemConsumeType</t>
+  </si>
+  <si>
+    <t>消耗品类型</t>
+  </si>
+  <si>
+    <t>GetGold</t>
+  </si>
+  <si>
+    <t>获得金币值</t>
+  </si>
+  <si>
+    <t>GetExp</t>
+  </si>
+  <si>
+    <t>获得经验值</t>
+  </si>
+  <si>
+    <t>BaoXian</t>
+  </si>
+  <si>
+    <t>随机宝箱</t>
+  </si>
+  <si>
+    <t>ItemEquipmentType</t>
+  </si>
+  <si>
+    <t>装备类型</t>
+  </si>
+  <si>
+    <t>Toukui</t>
+  </si>
+  <si>
+    <t>头盔</t>
+  </si>
+  <si>
+    <t>Yifu</t>
+  </si>
+  <si>
+    <t>衣服</t>
+  </si>
+  <si>
+    <t>Kuzi</t>
+  </si>
+  <si>
+    <t>裤子</t>
+  </si>
+  <si>
+    <t>Xiezi</t>
+  </si>
+  <si>
+    <t>鞋子</t>
+  </si>
+  <si>
+    <t>Xianglian</t>
+  </si>
+  <si>
+    <t>项链</t>
+  </si>
+  <si>
+    <t>Wuqi</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>EquipSlotType</t>
+  </si>
+  <si>
+    <t>装备穿戴插槽</t>
+  </si>
+  <si>
+    <t>头盔孔位</t>
+  </si>
+  <si>
+    <t>衣服孔位</t>
+  </si>
+  <si>
+    <t>裤子孔位</t>
+  </si>
+  <si>
+    <t>鞋子孔位</t>
+  </si>
+  <si>
+    <t>项链孔位</t>
+  </si>
+  <si>
+    <t>Wuqi_1</t>
+  </si>
+  <si>
+    <t>1号武器孔位</t>
+  </si>
+  <si>
+    <t>Wuqi_2</t>
+  </si>
+  <si>
+    <t>2号武器孔位(危境有个英雄可以装2个武器)</t>
   </si>
 </sst>
 </file>
@@ -720,7 +843,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -735,6 +858,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1055,19 +1181,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" outlineLevelRow="2"/>
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="2" max="2" width="21.625" customWidth="1"/>
     <col min="3" max="3" width="20.75" customWidth="1"/>
     <col min="4" max="4" width="14.1333333333333" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="9.38333333333333" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="18.6333333333333" customWidth="1"/>
     <col min="10" max="10" width="12.1333333333333" customWidth="1"/>
-    <col min="11" max="11" width="15.1333333333333" customWidth="1"/>
+    <col min="11" max="11" width="35.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1155,6 +1281,263 @@
         <v>18</v>
       </c>
       <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="8:11">
+      <c r="H5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="8:11">
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="8:11">
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="8:11">
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="8:11">
+      <c r="H11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="8:11">
+      <c r="H12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
+      </c>
+      <c r="K12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="8:11">
+      <c r="H13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13">
+        <v>4</v>
+      </c>
+      <c r="K13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="8:11">
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14">
+        <v>5</v>
+      </c>
+      <c r="K14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="8:11">
+      <c r="H15" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15">
+        <v>6</v>
+      </c>
+      <c r="K15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="8:11">
+      <c r="H17" t="s">
+        <v>39</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="8:11">
+      <c r="H18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="8:11">
+      <c r="H19" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19">
+        <v>4</v>
+      </c>
+      <c r="K19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="8:11">
+      <c r="H20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20">
+        <v>5</v>
+      </c>
+      <c r="K20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="8:11">
+      <c r="H21" t="s">
+        <v>56</v>
+      </c>
+      <c r="J21">
+        <v>6</v>
+      </c>
+      <c r="K21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="8:11">
+      <c r="H22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J22">
+        <v>7</v>
+      </c>
+      <c r="K22" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -197,10 +197,7 @@
     <t>项链孔位</t>
   </si>
   <si>
-    <t>Wuqi_1</t>
-  </si>
-  <si>
-    <t>1号武器孔位</t>
+    <t>武器孔位</t>
   </si>
   <si>
     <t>Wuqi_2</t>
@@ -1519,24 +1516,24 @@
     </row>
     <row r="21" spans="8:11">
       <c r="H21" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="J21">
         <v>6</v>
       </c>
       <c r="K21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="8:11">
       <c r="H22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J22">
         <v>7</v>
       </c>
       <c r="K22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>装备穿戴插槽</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
   <si>
     <t>头盔孔位</t>
@@ -1178,7 +1181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -1447,7 +1450,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="2:11">
+    <row r="16" spans="2:10">
       <c r="B16" t="s">
         <v>49</v>
       </c>
@@ -1461,21 +1464,18 @@
         <v>50</v>
       </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16" t="s">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="8:11">
       <c r="H17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" t="s">
         <v>52</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="18" spans="8:11">
       <c r="H18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" t="s">
         <v>53</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="19" spans="8:11">
       <c r="H19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" t="s">
         <v>54</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="20" spans="8:11">
       <c r="H20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K20" t="s">
         <v>55</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="21" spans="8:11">
       <c r="H21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K21" t="s">
         <v>56</v>
@@ -1527,13 +1527,24 @@
     </row>
     <row r="22" spans="8:11">
       <c r="H22" t="s">
+        <v>47</v>
+      </c>
+      <c r="J22">
+        <v>6</v>
+      </c>
+      <c r="K22" t="s">
         <v>57</v>
       </c>
-      <c r="J22">
+    </row>
+    <row r="23" spans="8:11">
+      <c r="H23" t="s">
+        <v>58</v>
+      </c>
+      <c r="J23">
         <v>7</v>
       </c>
-      <c r="K22" t="s">
-        <v>58</v>
+      <c r="K23" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -92,6 +92,9 @@
     <t>道具类型</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>Consume</t>
   </si>
   <si>
@@ -134,6 +137,12 @@
     <t>随机宝箱</t>
   </si>
   <si>
+    <t>HeroExp</t>
+  </si>
+  <si>
+    <t>英雄经验</t>
+  </si>
+  <si>
     <t>ItemEquipmentType</t>
   </si>
   <si>
@@ -180,9 +189,6 @@
   </si>
   <si>
     <t>装备穿戴插槽</t>
-  </si>
-  <si>
-    <t>None</t>
   </si>
   <si>
     <t>头盔孔位</t>
@@ -1181,7 +1187,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -1282,7 +1288,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1299,252 +1305,287 @@
         <v>21</v>
       </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="8:11">
       <c r="H5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
         <v>23</v>
       </c>
-      <c r="J5">
+    </row>
+    <row r="6" spans="8:11">
+      <c r="H6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6">
         <v>2</v>
       </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="8:11">
-      <c r="H6" t="s">
+      <c r="K6" t="s">
         <v>25</v>
       </c>
-      <c r="J6">
+    </row>
+    <row r="7" spans="8:11">
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7">
         <v>3</v>
       </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11">
-      <c r="B7" t="s">
+      <c r="K7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="b">
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="b">
         <v>0</v>
       </c>
-      <c r="D7" t="b">
+      <c r="D8" t="b">
         <v>1</v>
       </c>
-      <c r="F7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="F8" t="s">
         <v>29</v>
       </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="8:11">
       <c r="H8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J8">
-        <v>2</v>
-      </c>
-      <c r="K8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="8:11">
       <c r="H9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="8:11">
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10" t="s">
         <v>33</v>
-      </c>
-      <c r="J9">
-        <v>3</v>
-      </c>
-      <c r="K9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="11" spans="8:11">
       <c r="H11" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="8:11">
       <c r="H12" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="8:11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
+      </c>
       <c r="H13" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="J13">
-        <v>4</v>
-      </c>
-      <c r="K13" t="s">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="8:11">
       <c r="H14" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="8:11">
       <c r="H15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="8:11">
       <c r="H16" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="K16" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="8:11">
       <c r="H17" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K17" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="8:11">
       <c r="H18" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K18" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="8:11">
       <c r="H19" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="8:11">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="J20">
-        <v>4</v>
-      </c>
-      <c r="K20" t="s">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="8:11">
       <c r="H21" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="8:11">
       <c r="H22" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="8:11">
       <c r="H23" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="8:11">
+      <c r="H24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="K24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="8:11">
+      <c r="H25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J25">
+        <v>5</v>
+      </c>
+      <c r="K25" t="s">
         <v>58</v>
       </c>
-      <c r="J23">
+    </row>
+    <row r="26" spans="8:11">
+      <c r="H26" t="s">
+        <v>50</v>
+      </c>
+      <c r="J26">
+        <v>6</v>
+      </c>
+      <c r="K26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="8:11">
+      <c r="H27" t="s">
+        <v>60</v>
+      </c>
+      <c r="J27">
         <v>7</v>
       </c>
-      <c r="K23" t="s">
-        <v>59</v>
+      <c r="K27" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
   <si>
     <t>##var</t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t>英雄经验</t>
+  </si>
+  <si>
+    <t>HeroHunshi</t>
+  </si>
+  <si>
+    <t>英雄魂石</t>
   </si>
   <si>
     <t>ItemEquipmentType</t>
@@ -1187,7 +1193,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -1405,35 +1411,35 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
-      <c r="B13" t="s">
+    <row r="13" spans="8:11">
+      <c r="H13" t="s">
         <v>38</v>
       </c>
-      <c r="C13" t="b">
+      <c r="J13">
+        <v>9</v>
+      </c>
+      <c r="K13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="b">
         <v>0</v>
       </c>
-      <c r="D13" t="b">
+      <c r="D14" t="b">
         <v>1</v>
       </c>
-      <c r="F13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="F14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" t="s">
         <v>21</v>
       </c>
-      <c r="J13">
+      <c r="J14">
         <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="8:11">
-      <c r="H14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" spans="8:11">
@@ -1441,7 +1447,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="s">
         <v>43</v>
@@ -1452,7 +1458,7 @@
         <v>44</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="s">
         <v>45</v>
@@ -1463,7 +1469,7 @@
         <v>46</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K17" t="s">
         <v>47</v>
@@ -1474,7 +1480,7 @@
         <v>48</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K18" t="s">
         <v>49</v>
@@ -1485,41 +1491,41 @@
         <v>50</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K19" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
-      <c r="B20" t="s">
+    <row r="20" spans="8:11">
+      <c r="H20" t="s">
         <v>52</v>
       </c>
-      <c r="C20" t="b">
+      <c r="J20">
+        <v>6</v>
+      </c>
+      <c r="K20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="b">
         <v>0</v>
       </c>
-      <c r="D20" t="b">
+      <c r="D21" t="b">
         <v>1</v>
       </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="F21" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" t="s">
         <v>21</v>
       </c>
-      <c r="J20">
+      <c r="J21">
         <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="8:11">
-      <c r="H21" t="s">
-        <v>40</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="22" spans="8:11">
@@ -1527,10 +1533,10 @@
         <v>42</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="8:11">
@@ -1538,10 +1544,10 @@
         <v>44</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="8:11">
@@ -1549,10 +1555,10 @@
         <v>46</v>
       </c>
       <c r="J24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="8:11">
@@ -1560,10 +1566,10 @@
         <v>48</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="8:11">
@@ -1571,21 +1577,32 @@
         <v>50</v>
       </c>
       <c r="J26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="8:11">
       <c r="H27" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K27" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="8:11">
+      <c r="H28" t="s">
+        <v>62</v>
+      </c>
+      <c r="J28">
+        <v>7</v>
+      </c>
+      <c r="K28" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="80">
   <si>
     <t>##var</t>
   </si>
@@ -219,6 +219,54 @@
   </si>
   <si>
     <t>2号武器孔位(危境有个英雄可以装2个武器)</t>
+  </si>
+  <si>
+    <t>SkillTargetType</t>
+  </si>
+  <si>
+    <t>技能目标类型</t>
+  </si>
+  <si>
+    <t>SelfPosition</t>
+  </si>
+  <si>
+    <t>立即释放,自身中心点范围</t>
+  </si>
+  <si>
+    <t>TargetPositon</t>
+  </si>
+  <si>
+    <t>立即释放,目标中心点范围</t>
+  </si>
+  <si>
+    <t>TargetOnly</t>
+  </si>
+  <si>
+    <t>单体指定目标</t>
+  </si>
+  <si>
+    <t>SelfOnly</t>
+  </si>
+  <si>
+    <t>单体指定自己</t>
+  </si>
+  <si>
+    <t>MulTarget</t>
+  </si>
+  <si>
+    <t>单体技能多个目标</t>
+  </si>
+  <si>
+    <t>AllTeam</t>
+  </si>
+  <si>
+    <t>全体队友</t>
+  </si>
+  <si>
+    <t>AllEnemy</t>
+  </si>
+  <si>
+    <t>全体敌人</t>
   </si>
 </sst>
 </file>
@@ -855,7 +903,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -873,6 +921,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1193,7 +1244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -1202,9 +1253,9 @@
     <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="12.875" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="18.6333333333333" customWidth="1"/>
-    <col min="10" max="10" width="12.1333333333333" customWidth="1"/>
+    <col min="8" max="8" width="14.75" customWidth="1"/>
+    <col min="9" max="9" width="5.875" customWidth="1"/>
+    <col min="10" max="10" width="5.75" customWidth="1"/>
     <col min="11" max="11" width="35.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1603,6 +1654,95 @@
       </c>
       <c r="K28" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1" spans="2:11">
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>65</v>
+      </c>
+      <c r="H29" t="s">
+        <v>66</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="8:11">
+      <c r="H30" t="s">
+        <v>68</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="8:11">
+      <c r="H31" t="s">
+        <v>70</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="8:11">
+      <c r="H32" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32">
+        <v>3</v>
+      </c>
+      <c r="K32" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="8:11">
+      <c r="H33" t="s">
+        <v>74</v>
+      </c>
+      <c r="J33">
+        <v>4</v>
+      </c>
+      <c r="K33" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="8:11">
+      <c r="H34" t="s">
+        <v>76</v>
+      </c>
+      <c r="J34">
+        <v>5</v>
+      </c>
+      <c r="K34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="8:11">
+      <c r="H35" t="s">
+        <v>78</v>
+      </c>
+      <c r="J35">
+        <v>6</v>
+      </c>
+      <c r="K35" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="94">
   <si>
     <t>##var</t>
   </si>
@@ -267,6 +267,48 @@
   </si>
   <si>
     <t>全体敌人</t>
+  </si>
+  <si>
+    <t>TaskTargetType</t>
+  </si>
+  <si>
+    <t>任务目标类型</t>
+  </si>
+  <si>
+    <t>PlayerLv</t>
+  </si>
+  <si>
+    <t>等级达到指定等级</t>
+  </si>
+  <si>
+    <t>KillMonster</t>
+  </si>
+  <si>
+    <t>击杀任意怪物</t>
+  </si>
+  <si>
+    <t>KillBOSS</t>
+  </si>
+  <si>
+    <t>击杀任意BOSS</t>
+  </si>
+  <si>
+    <t>KillMonsterId</t>
+  </si>
+  <si>
+    <t>杀怪</t>
+  </si>
+  <si>
+    <t>PassLeveld</t>
+  </si>
+  <si>
+    <t>通关指定关卡</t>
+  </si>
+  <si>
+    <t>CombatPower</t>
+  </si>
+  <si>
+    <t>战力达到多少</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -1745,6 +1787,84 @@
         <v>79</v>
       </c>
     </row>
+    <row r="36" spans="2:11">
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" t="s">
+        <v>82</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="8:11">
+      <c r="H37" t="s">
+        <v>84</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="8:11">
+      <c r="H38" t="s">
+        <v>86</v>
+      </c>
+      <c r="J38">
+        <v>3</v>
+      </c>
+      <c r="K38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="8:11">
+      <c r="H39" t="s">
+        <v>88</v>
+      </c>
+      <c r="J39">
+        <v>4</v>
+      </c>
+      <c r="K39" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="8:11">
+      <c r="H40" t="s">
+        <v>90</v>
+      </c>
+      <c r="J40">
+        <v>5</v>
+      </c>
+      <c r="K40" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="8:11">
+      <c r="H41" t="s">
+        <v>92</v>
+      </c>
+      <c r="J41">
+        <v>6</v>
+      </c>
+      <c r="K41" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="100">
   <si>
     <t>##var</t>
   </si>
@@ -267,6 +267,24 @@
   </si>
   <si>
     <t>全体敌人</t>
+  </si>
+  <si>
+    <t>TaskType</t>
+  </si>
+  <si>
+    <t>任务类型</t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>主线任务</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>支线任务</t>
   </si>
   <si>
     <t>TaskTargetType</t>
@@ -1286,7 +1304,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -1821,48 +1839,82 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="8:11">
+    <row r="38" spans="2:11">
+      <c r="B38" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>87</v>
+      </c>
       <c r="H38" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="8:11">
       <c r="H39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="8:11">
       <c r="H40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K40" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="8:11">
       <c r="H41" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J41">
+        <v>4</v>
+      </c>
+      <c r="K41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="8:11">
+      <c r="H42" t="s">
+        <v>96</v>
+      </c>
+      <c r="J42">
+        <v>5</v>
+      </c>
+      <c r="K42" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="8:11">
+      <c r="H43" t="s">
+        <v>98</v>
+      </c>
+      <c r="J43">
         <v>6</v>
       </c>
-      <c r="K41" t="s">
-        <v>93</v>
+      <c r="K43" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="108">
   <si>
     <t>##var</t>
   </si>
@@ -113,7 +113,7 @@
     <t>装备</t>
   </si>
   <si>
-    <t>ItemConsumeType</t>
+    <t>ItemSubType</t>
   </si>
   <si>
     <t>消耗品类型</t>
@@ -131,12 +131,36 @@
     <t>获得经验值</t>
   </si>
   <si>
-    <t>BaoXian</t>
+    <t>SuiJiBaoXian</t>
   </si>
   <si>
     <t>随机宝箱</t>
   </si>
   <si>
+    <t>ZiXuanBaoXian</t>
+  </si>
+  <si>
+    <t>自选宝箱</t>
+  </si>
+  <si>
+    <t>Type_5</t>
+  </si>
+  <si>
+    <t>使用后永久增加属性</t>
+  </si>
+  <si>
+    <t>Type_6</t>
+  </si>
+  <si>
+    <t>抽奖券</t>
+  </si>
+  <si>
+    <t>Type_7</t>
+  </si>
+  <si>
+    <t>副本入场券</t>
+  </si>
+  <si>
     <t>HeroExp</t>
   </si>
   <si>
@@ -149,10 +173,10 @@
     <t>英雄魂石</t>
   </si>
   <si>
-    <t>ItemEquipmentType</t>
-  </si>
-  <si>
-    <t>装备类型</t>
+    <t>Type_10</t>
+  </si>
+  <si>
+    <t>英雄碎片</t>
   </si>
   <si>
     <t>Toukui</t>
@@ -1304,7 +1328,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -1516,7 +1540,7 @@
         <v>36</v>
       </c>
       <c r="J12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K12" t="s">
         <v>37</v>
@@ -1527,30 +1551,21 @@
         <v>38</v>
       </c>
       <c r="J13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
-      <c r="B14" t="s">
+    <row r="14" spans="8:11">
+      <c r="H14" t="s">
         <v>40</v>
       </c>
-      <c r="C14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="J14">
+        <v>6</v>
+      </c>
+      <c r="K14" t="s">
         <v>41</v>
-      </c>
-      <c r="H14" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
       </c>
     </row>
     <row r="15" spans="8:11">
@@ -1558,7 +1573,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K15" t="s">
         <v>43</v>
@@ -1569,7 +1584,7 @@
         <v>44</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K16" t="s">
         <v>45</v>
@@ -1580,7 +1595,7 @@
         <v>46</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K17" t="s">
         <v>47</v>
@@ -1591,7 +1606,7 @@
         <v>48</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K18" t="s">
         <v>49</v>
@@ -1602,7 +1617,7 @@
         <v>50</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>3001</v>
       </c>
       <c r="K19" t="s">
         <v>51</v>
@@ -1613,74 +1628,74 @@
         <v>52</v>
       </c>
       <c r="J20">
-        <v>6</v>
+        <v>3002</v>
       </c>
       <c r="K20" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="2:10">
-      <c r="B21" t="s">
+    <row r="21" spans="8:11">
+      <c r="H21" t="s">
         <v>54</v>
       </c>
-      <c r="C21" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="J21">
+        <v>3003</v>
+      </c>
+      <c r="K21" t="s">
         <v>55</v>
-      </c>
-      <c r="H21" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
       </c>
     </row>
     <row r="22" spans="8:11">
       <c r="H22" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>3004</v>
       </c>
       <c r="K22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="8:11">
       <c r="H23" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>3005</v>
       </c>
       <c r="K23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="8:11">
       <c r="H24" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>3006</v>
       </c>
       <c r="K24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="8:11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>63</v>
+      </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="J25">
-        <v>4</v>
-      </c>
-      <c r="K25" t="s">
-        <v>59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="8:11">
@@ -1688,10 +1703,10 @@
         <v>50</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="8:11">
@@ -1699,87 +1714,87 @@
         <v>52</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K27" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="8:11">
       <c r="H28" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="J28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K28" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1" spans="2:11">
-      <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" t="s">
-        <v>65</v>
-      </c>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="8:11">
       <c r="H29" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K29" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="30" spans="8:11">
       <c r="H30" t="s">
+        <v>58</v>
+      </c>
+      <c r="J30">
+        <v>5</v>
+      </c>
+      <c r="K30" t="s">
         <v>68</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="31" spans="8:11">
       <c r="H31" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K31" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="8:11">
       <c r="H32" t="s">
+        <v>70</v>
+      </c>
+      <c r="J32">
+        <v>7</v>
+      </c>
+      <c r="K32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1" spans="2:11">
+      <c r="B33" t="s">
         <v>72</v>
       </c>
-      <c r="J32">
-        <v>3</v>
-      </c>
-      <c r="K32" t="s">
+      <c r="C33" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="33" spans="8:11">
       <c r="H33" t="s">
         <v>74</v>
       </c>
       <c r="J33">
-        <v>4</v>
-      </c>
-      <c r="K33" t="s">
+        <v>0</v>
+      </c>
+      <c r="K33" s="6" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1788,7 +1803,7 @@
         <v>76</v>
       </c>
       <c r="J34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K34" t="s">
         <v>77</v>
@@ -1799,108 +1814,108 @@
         <v>78</v>
       </c>
       <c r="J35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K35" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="2:11">
-      <c r="B36" t="s">
+    <row r="36" spans="8:11">
+      <c r="H36" t="s">
         <v>80</v>
       </c>
-      <c r="C36" t="b">
-        <v>0</v>
-      </c>
-      <c r="D36" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="J36">
+        <v>3</v>
+      </c>
+      <c r="K36" t="s">
         <v>81</v>
-      </c>
-      <c r="H36" t="s">
-        <v>82</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-      <c r="K36" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="37" spans="8:11">
       <c r="H37" t="s">
+        <v>82</v>
+      </c>
+      <c r="J37">
+        <v>4</v>
+      </c>
+      <c r="K37" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="8:11">
+      <c r="H38" t="s">
         <v>84</v>
       </c>
-      <c r="J37">
-        <v>2</v>
-      </c>
-      <c r="K37" t="s">
+      <c r="J38">
+        <v>5</v>
+      </c>
+      <c r="K38" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11">
-      <c r="B38" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" t="s">
-        <v>87</v>
-      </c>
-      <c r="H38" t="s">
-        <v>88</v>
-      </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
-      <c r="K38" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="39" spans="8:11">
       <c r="H39" t="s">
+        <v>86</v>
+      </c>
+      <c r="J39">
+        <v>6</v>
+      </c>
+      <c r="K39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11">
+      <c r="B40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>89</v>
+      </c>
+      <c r="H40" t="s">
         <v>90</v>
       </c>
-      <c r="J39">
-        <v>2</v>
-      </c>
-      <c r="K39" t="s">
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="40" spans="8:11">
-      <c r="H40" t="s">
-        <v>92</v>
-      </c>
-      <c r="J40">
-        <v>3</v>
-      </c>
-      <c r="K40" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="41" spans="8:11">
       <c r="H41" t="s">
+        <v>92</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11">
+      <c r="B42" t="s">
         <v>94</v>
       </c>
-      <c r="J41">
-        <v>4</v>
-      </c>
-      <c r="K41" t="s">
+      <c r="C42" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="42" spans="8:11">
       <c r="H42" t="s">
         <v>96</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K42" t="s">
         <v>97</v>
@@ -1911,10 +1926,54 @@
         <v>98</v>
       </c>
       <c r="J43">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K43" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="8:11">
+      <c r="H44" t="s">
+        <v>100</v>
+      </c>
+      <c r="J44">
+        <v>3</v>
+      </c>
+      <c r="K44" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="8:11">
+      <c r="H45" t="s">
+        <v>102</v>
+      </c>
+      <c r="J45">
+        <v>4</v>
+      </c>
+      <c r="K45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="8:11">
+      <c r="H46" t="s">
+        <v>104</v>
+      </c>
+      <c r="J46">
+        <v>5</v>
+      </c>
+      <c r="K46" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="8:11">
+      <c r="H47" t="s">
+        <v>106</v>
+      </c>
+      <c r="J47">
+        <v>6</v>
+      </c>
+      <c r="K47" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="114">
   <si>
     <t>##var</t>
   </si>
@@ -351,6 +351,24 @@
   </si>
   <si>
     <t>战力达到多少</t>
+  </si>
+  <si>
+    <t>StateType</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>AllDamageImmune</t>
+  </si>
+  <si>
+    <t>免疫所有伤害</t>
+  </si>
+  <si>
+    <t>PhysicalImmune</t>
+  </si>
+  <si>
+    <t>免疫物理攻击</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +1346,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -1976,6 +1994,48 @@
         <v>107</v>
       </c>
     </row>
+    <row r="48" spans="2:10">
+      <c r="B48" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" t="b">
+        <v>1</v>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>109</v>
+      </c>
+      <c r="H48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="8:11">
+      <c r="H49" t="s">
+        <v>110</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="8:11">
+      <c r="H50" t="s">
+        <v>112</v>
+      </c>
+      <c r="J50">
+        <v>2</v>
+      </c>
+      <c r="K50" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -173,7 +173,7 @@
     <t>英雄魂石</t>
   </si>
   <si>
-    <t>Type_10</t>
+    <t>HeroShard</t>
   </si>
   <si>
     <t>英雄碎片</t>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="152">
   <si>
     <t>##var</t>
   </si>
@@ -243,6 +243,120 @@
   </si>
   <si>
     <t>2号武器孔位(危境有个英雄可以装2个武器)</t>
+  </si>
+  <si>
+    <t>SkillActType</t>
+  </si>
+  <si>
+    <t>技能攻击类型</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>普通攻击</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>技能攻击</t>
+  </si>
+  <si>
+    <t>DamageType</t>
+  </si>
+  <si>
+    <t>伤害类型</t>
+  </si>
+  <si>
+    <t>Physical</t>
+  </si>
+  <si>
+    <t>物理</t>
+  </si>
+  <si>
+    <t>Magical</t>
+  </si>
+  <si>
+    <t>魔法</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>暴击</t>
+  </si>
+  <si>
+    <t>Dodge</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>Recover</t>
+  </si>
+  <si>
+    <t>恢复</t>
+  </si>
+  <si>
+    <t>Immune</t>
+  </si>
+  <si>
+    <t>免疫</t>
+  </si>
+  <si>
+    <t>SkillType</t>
+  </si>
+  <si>
+    <t>技能类型</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+  </si>
+  <si>
+    <t>Passive</t>
+  </si>
+  <si>
+    <t>被动技能</t>
+  </si>
+  <si>
+    <t>PassiveSkillType</t>
+  </si>
+  <si>
+    <t>被动技能触发类型</t>
+  </si>
+  <si>
+    <t>无视</t>
+  </si>
+  <si>
+    <t>Type_1</t>
+  </si>
+  <si>
+    <t>受到伤害触发概率</t>
+  </si>
+  <si>
+    <t>Type_2</t>
+  </si>
+  <si>
+    <t>普通攻击触发概率</t>
+  </si>
+  <si>
+    <t>Type_3</t>
+  </si>
+  <si>
+    <t>血量低于多少百分比触发</t>
+  </si>
+  <si>
+    <t>Type_4</t>
+  </si>
+  <si>
+    <t>开始战斗就触发</t>
+  </si>
+  <si>
+    <t>队友血量低于多少百分比触发</t>
   </si>
   <si>
     <t>SkillTargetType</t>
@@ -1346,14 +1460,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
     <col min="3" max="3" width="20.75" customWidth="1"/>
     <col min="4" max="4" width="14.1333333333333" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="6" max="6" width="17.875" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="14.75" customWidth="1"/>
     <col min="9" max="9" width="5.875" customWidth="1"/>
@@ -1793,7 +1907,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1" spans="2:11">
+    <row r="33" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="B33" t="s">
         <v>72</v>
       </c>
@@ -1816,109 +1930,107 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="8:11">
+    <row r="34" customFormat="1" ht="16" customHeight="1" spans="8:11">
       <c r="H34" t="s">
         <v>76</v>
       </c>
       <c r="J34">
         <v>1</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K34" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="35" spans="8:11">
+    <row r="35" customFormat="1" ht="16" customHeight="1" spans="2:11">
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>79</v>
+      </c>
       <c r="H35" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="J35">
-        <v>2</v>
-      </c>
-      <c r="K35" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="8:11">
+        <v>0</v>
+      </c>
+      <c r="K35" s="6"/>
+    </row>
+    <row r="36" customFormat="1" ht="16" customHeight="1" spans="8:11">
       <c r="H36" t="s">
         <v>80</v>
       </c>
       <c r="J36">
-        <v>3</v>
-      </c>
-      <c r="K36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K36" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="8:11">
+    <row r="37" customFormat="1" ht="16" customHeight="1" spans="8:11">
       <c r="H37" t="s">
         <v>82</v>
       </c>
       <c r="J37">
-        <v>4</v>
-      </c>
-      <c r="K37" t="s">
+        <v>2</v>
+      </c>
+      <c r="K37" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="8:11">
+    <row r="38" customFormat="1" ht="16" customHeight="1" spans="8:11">
       <c r="H38" t="s">
         <v>84</v>
       </c>
       <c r="J38">
-        <v>5</v>
-      </c>
-      <c r="K38" t="s">
+        <v>3</v>
+      </c>
+      <c r="K38" s="6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="8:11">
+    <row r="39" customFormat="1" ht="16" customHeight="1" spans="8:11">
       <c r="H39" t="s">
         <v>86</v>
       </c>
       <c r="J39">
+        <v>4</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" ht="16" customHeight="1" spans="8:11">
+      <c r="H40" t="s">
+        <v>88</v>
+      </c>
+      <c r="J40">
+        <v>5</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" ht="16" customHeight="1" spans="8:11">
+      <c r="H41" t="s">
+        <v>90</v>
+      </c>
+      <c r="J41">
         <v>6</v>
       </c>
-      <c r="K39" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11">
-      <c r="B40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" t="b">
-        <v>0</v>
-      </c>
-      <c r="D40" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" t="s">
-        <v>89</v>
-      </c>
-      <c r="H40" t="s">
-        <v>90</v>
-      </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-      <c r="K40" t="s">
+      <c r="K41" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="8:11">
-      <c r="H41" t="s">
+    <row r="42" customFormat="1" ht="16" customHeight="1" spans="2:11">
+      <c r="B42" t="s">
         <v>92</v>
-      </c>
-      <c r="J41">
-        <v>2</v>
-      </c>
-      <c r="K41" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
-      <c r="B42" t="s">
-        <v>94</v>
       </c>
       <c r="C42" t="b">
         <v>0</v>
@@ -1927,113 +2039,357 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
+        <v>93</v>
+      </c>
+      <c r="H42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" s="6"/>
+    </row>
+    <row r="43" customFormat="1" ht="16" customHeight="1" spans="8:11">
+      <c r="H43" t="s">
+        <v>94</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="H42" t="s">
+    </row>
+    <row r="44" customFormat="1" spans="8:11">
+      <c r="H44" t="s">
         <v>96</v>
       </c>
-      <c r="J42">
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" ht="16" customHeight="1" spans="2:11">
+      <c r="B45" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" t="b">
         <v>1</v>
       </c>
-      <c r="K42" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" spans="8:11">
-      <c r="H43" t="s">
-        <v>98</v>
-      </c>
-      <c r="J43">
+      <c r="F45" t="s">
+        <v>99</v>
+      </c>
+      <c r="H45" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" ht="16" customHeight="1" spans="8:11">
+      <c r="H46" t="s">
+        <v>101</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" ht="16" customHeight="1" spans="8:11">
+      <c r="H47" t="s">
+        <v>103</v>
+      </c>
+      <c r="J47">
         <v>2</v>
       </c>
-      <c r="K43" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="8:11">
-      <c r="H44" t="s">
-        <v>100</v>
-      </c>
-      <c r="J44">
+      <c r="K47" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" ht="16" customHeight="1" spans="8:11">
+      <c r="H48" t="s">
+        <v>105</v>
+      </c>
+      <c r="J48">
         <v>3</v>
       </c>
-      <c r="K44" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="45" spans="8:11">
-      <c r="H45" t="s">
-        <v>102</v>
-      </c>
-      <c r="J45">
+      <c r="K48" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" ht="16" customHeight="1" spans="8:11">
+      <c r="H49" t="s">
+        <v>107</v>
+      </c>
+      <c r="J49">
         <v>4</v>
       </c>
-      <c r="K45" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="46" spans="8:11">
-      <c r="H46" t="s">
-        <v>104</v>
-      </c>
-      <c r="J46">
+      <c r="K49" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" ht="16" customHeight="1" spans="8:11">
+      <c r="H50" t="s">
+        <v>38</v>
+      </c>
+      <c r="J50">
         <v>5</v>
       </c>
-      <c r="K46" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="8:11">
-      <c r="H47" t="s">
-        <v>106</v>
-      </c>
-      <c r="J47">
+      <c r="K50" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1" spans="2:11">
+      <c r="B51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>111</v>
+      </c>
+      <c r="H51" t="s">
+        <v>112</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="52" spans="8:11">
+      <c r="H52" t="s">
+        <v>114</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" spans="8:11">
+      <c r="H53" t="s">
+        <v>116</v>
+      </c>
+      <c r="J53">
+        <v>2</v>
+      </c>
+      <c r="K53" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="8:11">
+      <c r="H54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J54">
+        <v>3</v>
+      </c>
+      <c r="K54" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="8:11">
+      <c r="H55" t="s">
+        <v>120</v>
+      </c>
+      <c r="J55">
+        <v>4</v>
+      </c>
+      <c r="K55" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" spans="8:11">
+      <c r="H56" t="s">
+        <v>122</v>
+      </c>
+      <c r="J56">
+        <v>5</v>
+      </c>
+      <c r="K56" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" spans="8:11">
+      <c r="H57" t="s">
+        <v>124</v>
+      </c>
+      <c r="J57">
         <v>6</v>
       </c>
-      <c r="K47" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10">
-      <c r="B48" t="s">
-        <v>108</v>
-      </c>
-      <c r="C48" t="b">
+      <c r="K57" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
+      <c r="B58" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" t="b">
+        <v>0</v>
+      </c>
+      <c r="D58" t="b">
         <v>1</v>
       </c>
-      <c r="D48" t="b">
+      <c r="F58" t="s">
+        <v>127</v>
+      </c>
+      <c r="H58" t="s">
+        <v>128</v>
+      </c>
+      <c r="J58">
         <v>1</v>
       </c>
-      <c r="F48" t="s">
-        <v>109</v>
-      </c>
-      <c r="H48" t="s">
+      <c r="K58" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="59" spans="8:11">
+      <c r="H59" t="s">
+        <v>130</v>
+      </c>
+      <c r="J59">
+        <v>2</v>
+      </c>
+      <c r="K59" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11">
+      <c r="B60" t="s">
+        <v>132</v>
+      </c>
+      <c r="C60" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="s">
+        <v>133</v>
+      </c>
+      <c r="H60" t="s">
+        <v>134</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="61" spans="8:11">
+      <c r="H61" t="s">
+        <v>136</v>
+      </c>
+      <c r="J61">
+        <v>2</v>
+      </c>
+      <c r="K61" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="62" spans="8:11">
+      <c r="H62" t="s">
+        <v>138</v>
+      </c>
+      <c r="J62">
+        <v>3</v>
+      </c>
+      <c r="K62" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="63" spans="8:11">
+      <c r="H63" t="s">
+        <v>140</v>
+      </c>
+      <c r="J63">
+        <v>4</v>
+      </c>
+      <c r="K63" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" spans="8:11">
+      <c r="H64" t="s">
+        <v>142</v>
+      </c>
+      <c r="J64">
+        <v>5</v>
+      </c>
+      <c r="K64" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="65" spans="8:11">
+      <c r="H65" t="s">
+        <v>144</v>
+      </c>
+      <c r="J65">
+        <v>6</v>
+      </c>
+      <c r="K65" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10">
+      <c r="B66" t="s">
+        <v>146</v>
+      </c>
+      <c r="C66" t="b">
+        <v>1</v>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>147</v>
+      </c>
+      <c r="H66" t="s">
         <v>21</v>
       </c>
-      <c r="J48">
+      <c r="J66">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="8:11">
-      <c r="H49" t="s">
-        <v>110</v>
-      </c>
-      <c r="J49">
+    <row r="67" spans="8:11">
+      <c r="H67" t="s">
+        <v>148</v>
+      </c>
+      <c r="J67">
         <v>1</v>
       </c>
-      <c r="K49" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" spans="8:11">
-      <c r="H50" t="s">
-        <v>112</v>
-      </c>
-      <c r="J50">
+      <c r="K67" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" spans="8:11">
+      <c r="H68" t="s">
+        <v>150</v>
+      </c>
+      <c r="J68">
         <v>2</v>
       </c>
-      <c r="K50" t="s">
-        <v>113</v>
+      <c r="K68" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -323,7 +323,7 @@
     <t>被动技能</t>
   </si>
   <si>
-    <t>PassiveSkillType</t>
+    <t>SkillPassiveType</t>
   </si>
   <si>
     <t>被动技能触发类型</t>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="153">
   <si>
     <t>##var</t>
   </si>
@@ -332,28 +332,31 @@
     <t>无视</t>
   </si>
   <si>
-    <t>Type_1</t>
+    <t>OnDamagedByChance</t>
   </si>
   <si>
     <t>受到伤害触发概率</t>
   </si>
   <si>
-    <t>Type_2</t>
+    <t>OnNormalAttackByChance</t>
   </si>
   <si>
     <t>普通攻击触发概率</t>
   </si>
   <si>
-    <t>Type_3</t>
+    <t>OnSelfHpBelowPercent</t>
   </si>
   <si>
     <t>血量低于多少百分比触发</t>
   </si>
   <si>
-    <t>Type_4</t>
+    <t>OnBattleStart</t>
   </si>
   <si>
     <t>开始战斗就触发</t>
+  </si>
+  <si>
+    <t>OnTeamHpBelowPercent</t>
   </si>
   <si>
     <t>队友血量低于多少百分比触发</t>
@@ -1469,7 +1472,7 @@
     <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="17.875" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="14.75" customWidth="1"/>
+    <col min="8" max="8" width="22.375" customWidth="1"/>
     <col min="9" max="9" width="5.875" customWidth="1"/>
     <col min="10" max="10" width="5.75" customWidth="1"/>
     <col min="11" max="11" width="35.875" customWidth="1"/>
@@ -2140,18 +2143,18 @@
     </row>
     <row r="50" customFormat="1" ht="16" customHeight="1" spans="8:11">
       <c r="H50" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="J50">
         <v>5</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1" spans="2:11">
       <c r="B51" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C51" t="b">
         <v>0</v>
@@ -2160,87 +2163,87 @@
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H51" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J51">
         <v>0</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="8:11">
       <c r="H52" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J52">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="8:11">
       <c r="H53" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J53">
         <v>2</v>
       </c>
       <c r="K53" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="8:11">
       <c r="H54" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J54">
         <v>3</v>
       </c>
       <c r="K54" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="8:11">
       <c r="H55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J55">
         <v>4</v>
       </c>
       <c r="K55" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="8:11">
       <c r="H56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J56">
         <v>5</v>
       </c>
       <c r="K56" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="8:11">
       <c r="H57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J57">
         <v>6</v>
       </c>
       <c r="K57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="2:11">
       <c r="B58" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C58" t="b">
         <v>0</v>
@@ -2249,32 +2252,32 @@
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H58" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="8:11">
       <c r="H59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J59">
         <v>2</v>
       </c>
       <c r="K59" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="2:11">
       <c r="B60" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C60" t="b">
         <v>0</v>
@@ -2283,76 +2286,76 @@
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J60">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="8:11">
       <c r="H61" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J61">
         <v>2</v>
       </c>
       <c r="K61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="8:11">
       <c r="H62" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J62">
         <v>3</v>
       </c>
       <c r="K62" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="8:11">
       <c r="H63" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J63">
         <v>4</v>
       </c>
       <c r="K63" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="64" spans="8:11">
       <c r="H64" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J64">
         <v>5</v>
       </c>
       <c r="K64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="8:11">
       <c r="H65" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J65">
         <v>6</v>
       </c>
       <c r="K65" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="2:10">
       <c r="B66" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C66" t="b">
         <v>1</v>
@@ -2361,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H66" t="s">
         <v>21</v>
@@ -2372,24 +2375,24 @@
     </row>
     <row r="67" spans="8:11">
       <c r="H67" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J67">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="8:11">
       <c r="H68" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J68">
         <v>2</v>
       </c>
       <c r="K68" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="155">
   <si>
     <t>##var</t>
   </si>
@@ -486,6 +486,12 @@
   </si>
   <si>
     <t>免疫物理攻击</t>
+  </si>
+  <si>
+    <t>Invincibility</t>
+  </si>
+  <si>
+    <t>无敌</t>
   </si>
 </sst>
 </file>
@@ -1463,7 +1469,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -2395,6 +2401,17 @@
         <v>152</v>
       </c>
     </row>
+    <row r="69" spans="8:11">
+      <c r="H69" t="s">
+        <v>153</v>
+      </c>
+      <c r="J69">
+        <v>3</v>
+      </c>
+      <c r="K69" t="s">
+        <v>154</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="153">
   <si>
     <t>##var</t>
   </si>
@@ -479,19 +479,13 @@
     <t>AllDamageImmune</t>
   </si>
   <si>
-    <t>免疫所有伤害</t>
+    <t>无敌</t>
   </si>
   <si>
     <t>PhysicalImmune</t>
   </si>
   <si>
     <t>免疫物理攻击</t>
-  </si>
-  <si>
-    <t>Invincibility</t>
-  </si>
-  <si>
-    <t>无敌</t>
   </si>
 </sst>
 </file>
@@ -1469,7 +1463,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -2401,17 +2395,6 @@
         <v>152</v>
       </c>
     </row>
-    <row r="69" spans="8:11">
-      <c r="H69" t="s">
-        <v>153</v>
-      </c>
-      <c r="J69">
-        <v>3</v>
-      </c>
-      <c r="K69" t="s">
-        <v>154</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="157">
   <si>
     <t>##var</t>
   </si>
@@ -486,6 +486,18 @@
   </si>
   <si>
     <t>免疫物理攻击</t>
+  </si>
+  <si>
+    <t>MagicalImmune</t>
+  </si>
+  <si>
+    <t>免疫魔法攻击</t>
+  </si>
+  <si>
+    <t>Taunt</t>
+  </si>
+  <si>
+    <t>嘲讽</t>
   </si>
 </sst>
 </file>
@@ -1463,7 +1475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -2395,6 +2407,28 @@
         <v>152</v>
       </c>
     </row>
+    <row r="69" spans="8:11">
+      <c r="H69" t="s">
+        <v>153</v>
+      </c>
+      <c r="J69">
+        <v>3</v>
+      </c>
+      <c r="K69" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="70" spans="8:11">
+      <c r="H70" t="s">
+        <v>155</v>
+      </c>
+      <c r="J70">
+        <v>4</v>
+      </c>
+      <c r="K70" t="s">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="159">
   <si>
     <t>##var</t>
   </si>
@@ -498,6 +498,12 @@
   </si>
   <si>
     <t>嘲讽</t>
+  </si>
+  <si>
+    <t>Stun</t>
+  </si>
+  <si>
+    <t>眩晕</t>
   </si>
 </sst>
 </file>
@@ -1475,7 +1481,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -2412,7 +2418,7 @@
         <v>153</v>
       </c>
       <c r="J69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K69" t="s">
         <v>154</v>
@@ -2423,10 +2429,21 @@
         <v>155</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K70" t="s">
         <v>156</v>
+      </c>
+    </row>
+    <row r="71" spans="8:11">
+      <c r="H71" t="s">
+        <v>157</v>
+      </c>
+      <c r="J71">
+        <v>16</v>
+      </c>
+      <c r="K71" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="161">
   <si>
     <t>##var</t>
   </si>
@@ -504,6 +504,12 @@
   </si>
   <si>
     <t>眩晕</t>
+  </si>
+  <si>
+    <t>Freeze</t>
+  </si>
+  <si>
+    <t>冰冻</t>
   </si>
 </sst>
 </file>
@@ -1481,7 +1487,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -2446,6 +2452,17 @@
         <v>158</v>
       </c>
     </row>
+    <row r="72" spans="8:11">
+      <c r="H72" t="s">
+        <v>159</v>
+      </c>
+      <c r="J72">
+        <v>32</v>
+      </c>
+      <c r="K72" t="s">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Unity/Assets/Config/Excel/__enums__.xlsx
+++ b/Unity/Assets/Config/Excel/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="169">
   <si>
     <t>##var</t>
   </si>
@@ -510,6 +510,30 @@
   </si>
   <si>
     <t>冰冻</t>
+  </si>
+  <si>
+    <t>AchievementTargetType</t>
+  </si>
+  <si>
+    <t>成就目标类型</t>
+  </si>
+  <si>
+    <t>HaveHeroId</t>
+  </si>
+  <si>
+    <t>拥有指定英雄</t>
+  </si>
+  <si>
+    <t>HaveHeroValue</t>
+  </si>
+  <si>
+    <t>拥有英雄数量</t>
+  </si>
+  <si>
+    <t>HeroLv</t>
+  </si>
+  <si>
+    <t>英雄最高等级</t>
   </si>
 </sst>
 </file>
@@ -1487,7 +1511,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
@@ -1588,7 +1612,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1608,7 +1632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:11">
+    <row r="5" spans="1:12">
       <c r="H5" s="5" t="s">
         <v>22</v>
       </c>
@@ -1619,7 +1643,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="8:11">
+    <row r="6" spans="1:12">
       <c r="H6" s="5" t="s">
         <v>24</v>
       </c>
@@ -1630,7 +1654,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="8:11">
+    <row r="7" spans="1:12">
       <c r="H7" t="s">
         <v>26</v>
       </c>
@@ -1641,7 +1665,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="1:12">
       <c r="B8" t="s">
         <v>28</v>
       </c>
@@ -1661,7 +1685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="8:11">
+    <row r="9" spans="1:12">
       <c r="H9" t="s">
         <v>30</v>
       </c>
@@ -1672,7 +1696,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="8:11">
+    <row r="10" spans="1:12">
       <c r="H10" t="s">
         <v>32</v>
       </c>
@@ -1683,7 +1707,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="8:11">
+    <row r="11" spans="1:12">
       <c r="H11" t="s">
         <v>34</v>
       </c>
@@ -1694,7 +1718,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="8:11">
+    <row r="12" spans="1:12">
       <c r="H12" t="s">
         <v>36</v>
       </c>
@@ -1705,7 +1729,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="8:11">
+    <row r="13" spans="1:12">
       <c r="H13" t="s">
         <v>38</v>
       </c>
@@ -1716,7 +1740,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="8:11">
+    <row r="14" spans="1:12">
       <c r="H14" t="s">
         <v>40</v>
       </c>
@@ -1727,7 +1751,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="8:11">
+    <row r="15" spans="1:12">
       <c r="H15" t="s">
         <v>42</v>
       </c>
@@ -1738,7 +1762,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="8:11">
+    <row r="16" spans="1:12">
       <c r="H16" t="s">
         <v>44</v>
       </c>
@@ -1749,7 +1773,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="8:11">
+    <row r="17" spans="2:11">
       <c r="H17" t="s">
         <v>46</v>
       </c>
@@ -1760,7 +1784,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="8:11">
+    <row r="18" spans="2:11">
       <c r="H18" t="s">
         <v>48</v>
       </c>
@@ -1771,7 +1795,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="8:11">
+    <row r="19" spans="2:11">
       <c r="H19" t="s">
         <v>50</v>
       </c>
@@ -1782,7 +1806,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="8:11">
+    <row r="20" spans="2:11">
       <c r="H20" t="s">
         <v>52</v>
       </c>
@@ -1793,7 +1817,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="8:11">
+    <row r="21" spans="2:11">
       <c r="H21" t="s">
         <v>54</v>
       </c>
@@ -1804,7 +1828,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="8:11">
+    <row r="22" spans="2:11">
       <c r="H22" t="s">
         <v>56</v>
       </c>
@@ -1815,7 +1839,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="8:11">
+    <row r="23" spans="2:11">
       <c r="H23" t="s">
         <v>58</v>
       </c>
@@ -1826,7 +1850,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="8:11">
+    <row r="24" spans="2:11">
       <c r="H24" t="s">
         <v>60</v>
       </c>
@@ -1837,7 +1861,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:11">
       <c r="B25" t="s">
         <v>62</v>
       </c>
@@ -1857,7 +1881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="8:11">
+    <row r="26" spans="2:11">
       <c r="H26" t="s">
         <v>50</v>
       </c>
@@ -1868,7 +1892,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="8:11">
+    <row r="27" spans="2:11">
       <c r="H27" t="s">
         <v>52</v>
       </c>
@@ -1879,7 +1903,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="8:11">
+    <row r="28" spans="2:11">
       <c r="H28" t="s">
         <v>54</v>
       </c>
@@ -1890,7 +1914,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="8:11">
+    <row r="29" spans="2:11">
       <c r="H29" t="s">
         <v>56</v>
       </c>
@@ -1901,7 +1925,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="8:11">
+    <row r="30" spans="2:11">
       <c r="H30" t="s">
         <v>58</v>
       </c>
@@ -1912,7 +1936,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="8:11">
+    <row r="31" spans="2:11">
       <c r="H31" t="s">
         <v>60</v>
       </c>
@@ -1923,7 +1947,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="8:11">
+    <row r="32" spans="2:11">
       <c r="H32" t="s">
         <v>70</v>
       </c>
@@ -1957,7 +1981,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="34" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H34" t="s">
         <v>76</v>
       </c>
@@ -1989,7 +2013,7 @@
       </c>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="36" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H36" t="s">
         <v>80</v>
       </c>
@@ -2000,7 +2024,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="37" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H37" t="s">
         <v>82</v>
       </c>
@@ -2011,7 +2035,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="38" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H38" t="s">
         <v>84</v>
       </c>
@@ -2022,7 +2046,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="39" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H39" t="s">
         <v>86</v>
       </c>
@@ -2033,7 +2057,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="40" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H40" t="s">
         <v>88</v>
       </c>
@@ -2044,7 +2068,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="41" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H41" t="s">
         <v>90</v>
       </c>
@@ -2076,7 +2100,7 @@
       </c>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="43" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H43" t="s">
         <v>94</v>
       </c>
@@ -2087,7 +2111,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" customFormat="1" spans="8:11">
+    <row r="44" customFormat="1" spans="2:11">
       <c r="H44" t="s">
         <v>96</v>
       </c>
@@ -2121,7 +2145,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="46" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H46" t="s">
         <v>101</v>
       </c>
@@ -2132,7 +2156,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="47" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H47" t="s">
         <v>103</v>
       </c>
@@ -2143,7 +2167,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="48" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H48" t="s">
         <v>105</v>
       </c>
@@ -2154,7 +2178,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="49" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="49" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H49" t="s">
         <v>107</v>
       </c>
@@ -2165,7 +2189,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="16" customHeight="1" spans="8:11">
+    <row r="50" customFormat="1" ht="16" customHeight="1" spans="2:11">
       <c r="H50" t="s">
         <v>109</v>
       </c>
@@ -2199,7 +2223,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="8:11">
+    <row r="52" spans="2:11">
       <c r="H52" t="s">
         <v>115</v>
       </c>
@@ -2210,7 +2234,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="8:11">
+    <row r="53" spans="2:11">
       <c r="H53" t="s">
         <v>117</v>
       </c>
@@ -2221,7 +2245,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="8:11">
+    <row r="54" spans="2:11">
       <c r="H54" t="s">
         <v>119</v>
       </c>
@@ -2232,7 +2256,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="8:11">
+    <row r="55" spans="2:11">
       <c r="H55" t="s">
         <v>121</v>
       </c>
@@ -2243,7 +2267,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="8:11">
+    <row r="56" spans="2:11">
       <c r="H56" t="s">
         <v>123</v>
       </c>
@@ -2254,7 +2278,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="8:11">
+    <row r="57" spans="2:11">
       <c r="H57" t="s">
         <v>125</v>
       </c>
@@ -2288,7 +2312,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="59" spans="8:11">
+    <row r="59" spans="2:11">
       <c r="H59" t="s">
         <v>131</v>
       </c>
@@ -2322,7 +2346,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="61" spans="8:11">
+    <row r="61" spans="2:11">
       <c r="H61" t="s">
         <v>137</v>
       </c>
@@ -2333,7 +2357,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="8:11">
+    <row r="62" spans="2:11">
       <c r="H62" t="s">
         <v>139</v>
       </c>
@@ -2344,7 +2368,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="8:11">
+    <row r="63" spans="2:11">
       <c r="H63" t="s">
         <v>141</v>
       </c>
@@ -2355,7 +2379,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="64" spans="8:11">
+    <row r="64" spans="2:11">
       <c r="H64" t="s">
         <v>143</v>
       </c>
@@ -2366,7 +2390,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="65" spans="8:11">
+    <row r="65" spans="2:11">
       <c r="H65" t="s">
         <v>145</v>
       </c>
@@ -2377,7 +2401,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:11">
       <c r="B66" t="s">
         <v>147</v>
       </c>
@@ -2397,7 +2421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="8:11">
+    <row r="67" spans="2:11">
       <c r="H67" t="s">
         <v>149</v>
       </c>
@@ -2408,7 +2432,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" customFormat="1" spans="8:11">
+    <row r="68" customFormat="1" spans="2:11">
       <c r="H68" t="s">
         <v>151</v>
       </c>
@@ -2419,7 +2443,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="69" spans="8:11">
+    <row r="69" spans="2:11">
       <c r="H69" t="s">
         <v>153</v>
       </c>
@@ -2430,7 +2454,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="70" spans="8:11">
+    <row r="70" spans="2:11">
       <c r="H70" t="s">
         <v>155</v>
       </c>
@@ -2441,7 +2465,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="71" spans="8:11">
+    <row r="71" spans="2:11">
       <c r="H71" t="s">
         <v>157</v>
       </c>
@@ -2452,7 +2476,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="72" spans="8:11">
+    <row r="72" spans="2:11">
       <c r="H72" t="s">
         <v>159</v>
       </c>
@@ -2461,6 +2485,59 @@
       </c>
       <c r="K72" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="73" customFormat="1" spans="2:11">
+      <c r="B73" t="s">
+        <v>161</v>
+      </c>
+      <c r="C73" t="b">
+        <v>0</v>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" t="s">
+        <v>162</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="H74" t="s">
+        <v>163</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="K74" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11">
+      <c r="H75" t="s">
+        <v>165</v>
+      </c>
+      <c r="J75">
+        <v>2</v>
+      </c>
+      <c r="K75" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11">
+      <c r="H76" t="s">
+        <v>167</v>
+      </c>
+      <c r="J76">
+        <v>3</v>
+      </c>
+      <c r="K76" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
